--- a/Tes.xlsx
+++ b/Tes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanardiansyah/side-project/wablas-autorespond/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36F5558-7E7F-064E-88E1-A7D870471113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FE2E29-3A09-3342-AC7E-607E96D27065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="22440" windowWidth="38400" windowHeight="24020" xr2:uid="{D8983B48-1D71-7843-9035-0059D3DD5E7E}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="38400" windowHeight="24000" xr2:uid="{D8983B48-1D71-7843-9035-0059D3DD5E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="54">
-  <si>
-    <t>Nama Lengkap</t>
-  </si>
   <si>
     <t>Posisi</t>
   </si>
@@ -188,9 +185,6 @@
     <t>Yasinta Amalia</t>
   </si>
   <si>
-    <t>telpon</t>
-  </si>
-  <si>
     <t>Tiara Reza</t>
   </si>
   <si>
@@ -198,6 +192,12 @@
   </si>
   <si>
     <t>tes1@gmail.com</t>
+  </si>
+  <si>
+    <t>nama</t>
+  </si>
+  <si>
+    <t>phone</t>
   </si>
 </sst>
 </file>
@@ -637,64 +637,64 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
@@ -705,17 +705,17 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="F2" s="4">
         <v>76</v>
@@ -730,29 +730,29 @@
         <v>3</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="4">
         <v>760122090053</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S2" s="3"/>
       <c r="T2" s="7">
@@ -767,17 +767,17 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="4">
         <v>76</v>
@@ -792,29 +792,29 @@
         <v>3</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="7">
@@ -829,17 +829,17 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4">
         <v>76</v>
@@ -854,30 +854,30 @@
         <v>2</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T4" s="7">
         <v>6289692311560</v>
@@ -891,17 +891,17 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="4">
         <v>76</v>
@@ -916,22 +916,22 @@
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -947,17 +947,17 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="4">
         <v>76</v>
@@ -972,24 +972,24 @@
         <v>2</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -1005,17 +1005,17 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4">
         <v>76</v>
@@ -1030,24 +1030,24 @@
         <v>3</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -1063,17 +1063,17 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="4">
         <v>76</v>
@@ -1088,22 +1088,22 @@
         <v>2</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -1119,17 +1119,17 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4">
         <v>76</v>
@@ -1144,22 +1144,22 @@
         <v>2</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
